--- a/data/trans_dic/P25A$rendimiento-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,99</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 13,92</t>
+          <t>2,07; 14,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 26,49</t>
+          <t>9,15; 26,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,13</t>
+          <t>0,0; 19,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 20,78</t>
+          <t>3,72; 20,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 9,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 11,99</t>
+          <t>1,61; 11,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 20,07</t>
+          <t>7,85; 20,6</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,99</t>
+          <t>0,92; 8,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 8,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 17,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,55</t>
+          <t>0,0; 11,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,01</t>
+          <t>0,0; 21,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,27</t>
+          <t>1,38; 7,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,78</t>
+          <t>0,53; 5,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,69</t>
+          <t>1,01; 9,22</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,66</t>
+          <t>2,84; 16,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,67</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,09</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,92</t>
+          <t>0,0; 16,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,38</t>
+          <t>2,3; 13,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,81</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 8,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 15,68</t>
+          <t>4,74; 15,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,75</t>
+          <t>2,14; 13,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 27,21</t>
+          <t>5,0; 29,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,77</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 24,45</t>
+          <t>4,17; 24,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 11,32</t>
+          <t>2,78; 11,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 11,87</t>
+          <t>3,4; 11,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,68</t>
+          <t>3,51; 12,38</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 10,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 24,37</t>
+          <t>2,97; 25,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,16</t>
+          <t>0,0; 17,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,47</t>
+          <t>0,0; 23,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,04</t>
+          <t>1,21; 10,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,74</t>
+          <t>1,85; 14,76</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,74</t>
+          <t>0,0; 16,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,95</t>
+          <t>0,0; 21,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,81</t>
+          <t>1,19; 11,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 5,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,79</t>
+          <t>0,0; 14,72</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,82</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,38</t>
+          <t>1,97; 8,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,32 +1353,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,79</t>
+          <t>0,0; 17,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 8,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,32</t>
+          <t>0,76; 7,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,73</t>
+          <t>1,92; 6,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,53</t>
+          <t>0,95; 6,39</t>
         </is>
       </c>
     </row>
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,1</t>
+          <t>0,8; 7,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 6,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,8</t>
+          <t>1,11; 11,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,24</t>
+          <t>1,41; 13,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,63</t>
+          <t>0,0; 10,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,35</t>
+          <t>1,31; 6,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,01</t>
+          <t>1,65; 7,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,62</t>
+          <t>0,64; 5,75</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,88</t>
+          <t>2,06; 4,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,24</t>
+          <t>2,54; 5,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,42</t>
+          <t>3,39; 7,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,42</t>
+          <t>2,77; 8,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,66</t>
+          <t>1,69; 5,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,45</t>
+          <t>2,74; 7,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,01</t>
+          <t>2,65; 5,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,84</t>
+          <t>2,56; 4,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,54</t>
+          <t>3,51; 6,36</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5572</t>
+          <t>0; 5760</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>906; 11288</t>
+          <t>1676; 12142</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7037; 20915</t>
+          <t>7228; 21176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 10059</t>
+          <t>0; 7718</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1933; 10803</t>
+          <t>1935; 10734</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5666</t>
+          <t>0; 6551</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2573; 14526</t>
+          <t>1951; 14443</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11005; 26285</t>
+          <t>10282; 26971</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1033; 10231</t>
+          <t>1046; 9421</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6990</t>
+          <t>0; 6825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5801</t>
+          <t>0; 5918</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4467</t>
+          <t>0; 4414</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4517</t>
+          <t>0; 6600</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6154</t>
+          <t>0; 6392</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1900; 10159</t>
+          <t>1925; 11032</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>960; 8635</t>
+          <t>958; 9221</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1017; 8832</t>
+          <t>1027; 9372</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1786; 10618</t>
+          <t>1810; 10312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4669</t>
+          <t>0; 4049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5634</t>
+          <t>0; 5535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1795</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5873</t>
+          <t>0; 5421</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1755</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1739; 10430</t>
+          <t>1795; 10345</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7533</t>
+          <t>0; 7447</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5205</t>
+          <t>0; 4671</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6918</t>
+          <t>0; 6341</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4278; 16536</t>
+          <t>4998; 16201</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1831; 10231</t>
+          <t>1864; 11750</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1918; 10252</t>
+          <t>1884; 10931</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5939</t>
+          <t>0; 4293</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1833; 10922</t>
+          <t>1860; 10727</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2865; 12859</t>
+          <t>3162; 13318</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5125; 18034</t>
+          <t>5165; 17749</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4775; 16709</t>
+          <t>4625; 16313</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4271</t>
+          <t>0; 5055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>932; 7732</t>
+          <t>944; 8036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4981</t>
+          <t>0; 5182</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6034</t>
+          <t>0; 6194</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1800</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4793</t>
+          <t>0; 4975</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>952; 7759</t>
+          <t>937; 7999</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>914; 8172</t>
+          <t>904; 7203</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5871</t>
+          <t>0; 6369</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5202</t>
+          <t>0; 5235</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 8317</t>
+          <t>0; 7305</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6198</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1888</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>854; 7750</t>
+          <t>854; 7982</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4755</t>
+          <t>0; 5721</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8434</t>
+          <t>0; 9007</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6288</t>
+          <t>0; 6516</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3467; 15246</t>
+          <t>3202; 14466</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>901; 9785</t>
+          <t>907; 9783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5519</t>
+          <t>0; 5729</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6353</t>
+          <t>0; 7083</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6650</t>
+          <t>0; 7247</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>959; 9155</t>
+          <t>944; 9593</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4693; 17116</t>
+          <t>4896; 17776</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2077; 13796</t>
+          <t>2005; 13507</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>831; 8249</t>
+          <t>828; 8262</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1001; 9248</t>
+          <t>1046; 9531</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5477</t>
+          <t>0; 6127</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>797; 8516</t>
+          <t>798; 8112</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>962; 8861</t>
+          <t>942; 9047</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 6796</t>
+          <t>0; 6716</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2760; 13381</t>
+          <t>2755; 12930</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2477; 13821</t>
+          <t>3247; 15063</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1063; 9339</t>
+          <t>1062; 9542</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13128; 30466</t>
+          <t>12841; 29474</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19923; 42768</t>
+          <t>20728; 43390</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21916; 44924</t>
+          <t>20534; 43484</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7348; 21121</t>
+          <t>6940; 21806</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6864; 21879</t>
+          <t>6521; 20973</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9618; 25014</t>
+          <t>9209; 24915</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23317; 43831</t>
+          <t>23224; 43983</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30754; 58175</t>
+          <t>30736; 57019</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>35259; 61580</t>
+          <t>33082; 59840</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$rendimiento-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Provincia-trans_dic.xlsx
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,4</t>
+          <t>0,0; 13,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 14,97</t>
+          <t>2,08; 15,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 26,82</t>
+          <t>9,0; 26,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,28</t>
+          <t>0,0; 18,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 20,65</t>
+          <t>3,67; 20,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,85</t>
+          <t>0,0; 9,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,92</t>
+          <t>1,62; 13,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 20,6</t>
+          <t>8,16; 20,96</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,27</t>
+          <t>0,91; 8,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 8,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,07</t>
+          <t>0,0; 18,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,03</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,82</t>
+          <t>0,0; 21,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,9</t>
+          <t>0,75; 7,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,1</t>
+          <t>0,52; 4,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,22</t>
+          <t>1,0; 8,74</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 16,18</t>
+          <t>2,86; 16,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,54</t>
+          <t>0,0; 18,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 13,27</t>
+          <t>2,31; 12,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 6,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,36</t>
+          <t>0,0; 9,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 15,37</t>
+          <t>4,83; 15,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 13,49</t>
+          <t>2,02; 11,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 29,01</t>
+          <t>5,01; 27,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,23</t>
+          <t>0,0; 8,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 24,02</t>
+          <t>4,2; 23,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 11,73</t>
+          <t>2,56; 12,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 11,68</t>
+          <t>3,39; 11,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 12,38</t>
+          <t>3,6; 12,5</t>
         </is>
       </c>
     </row>
@@ -1123,22 +1123,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,03</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 25,33</t>
+          <t>2,98; 23,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,85</t>
+          <t>0,0; 13,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,07</t>
+          <t>0,0; 22,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,35</t>
+          <t>1,23; 10,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 14,76</t>
+          <t>1,9; 16,29</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 12,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,46</t>
+          <t>0,0; 15,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,86</t>
+          <t>0,0; 27,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 11,13</t>
+          <t>1,2; 10,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,45</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,72</t>
+          <t>0,0; 15,83</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,07</t>
+          <t>0,0; 7,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,9</t>
+          <t>1,91; 8,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,71</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,43</t>
+          <t>0,0; 17,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,71</t>
+          <t>0,0; 6,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,58</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,67</t>
+          <t>0,75; 7,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,99</t>
+          <t>1,84; 7,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,39</t>
+          <t>0,98; 6,03</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,96</t>
+          <t>0,76; 6,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,32</t>
+          <t>0,75; 7,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,0</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,11; 11,24</t>
+          <t>1,12; 11,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 13,52</t>
+          <t>1,44; 13,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,5</t>
+          <t>0,0; 10,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,14</t>
+          <t>1,29; 5,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,64</t>
+          <t>1,59; 7,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,75</t>
+          <t>0,64; 5,57</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,72</t>
+          <t>2,09; 4,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,32</t>
+          <t>2,63; 5,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,18</t>
+          <t>3,42; 7,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,7</t>
+          <t>2,81; 8,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,43</t>
+          <t>1,87; 5,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,42</t>
+          <t>2,92; 7,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,02</t>
+          <t>2,61; 5,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,74</t>
+          <t>2,64; 4,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,36</t>
+          <t>3,63; 6,53</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5760</t>
+          <t>0; 6475</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1676; 12142</t>
+          <t>1686; 12189</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7228; 21176</t>
+          <t>7106; 20779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7718</t>
+          <t>0; 7220</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1935; 10734</t>
+          <t>1910; 10469</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6551</t>
+          <t>0; 6019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1951; 14443</t>
+          <t>1965; 15991</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10282; 26971</t>
+          <t>10688; 27445</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1046; 9421</t>
+          <t>1034; 9500</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6825</t>
+          <t>0; 6203</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5918</t>
+          <t>0; 5891</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4414</t>
+          <t>0; 4742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6600</t>
+          <t>0; 4523</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6392</t>
+          <t>0; 6239</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1925; 11032</t>
+          <t>1050; 10289</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>958; 9221</t>
+          <t>943; 8301</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1027; 9372</t>
+          <t>1015; 8880</t>
         </is>
       </c>
     </row>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1810; 10312</t>
+          <t>1822; 10662</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4049</t>
+          <t>0; 3953</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5535</t>
+          <t>0; 5376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 6011</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1795; 10345</t>
+          <t>1802; 10089</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7447</t>
+          <t>0; 7409</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4671</t>
+          <t>0; 4674</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6341</t>
+          <t>0; 6857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4998; 16201</t>
+          <t>5098; 16140</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1864; 11750</t>
+          <t>1763; 10211</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1884; 10931</t>
+          <t>1887; 10452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4293</t>
+          <t>0; 4025</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1860; 10727</t>
+          <t>1877; 10501</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3162; 13318</t>
+          <t>2903; 13847</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5165; 17749</t>
+          <t>5149; 17389</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4625; 16313</t>
+          <t>4745; 16472</t>
         </is>
       </c>
     </row>
@@ -2518,22 +2518,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5055</t>
+          <t>0; 4589</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>944; 8036</t>
+          <t>944; 7386</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5182</t>
+          <t>0; 3937</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6194</t>
+          <t>0; 6144</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4975</t>
+          <t>0; 4790</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>937; 7999</t>
+          <t>953; 8068</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>904; 7203</t>
+          <t>929; 7949</t>
         </is>
       </c>
     </row>
@@ -2676,22 +2676,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6369</t>
+          <t>0; 6454</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5235</t>
+          <t>0; 5145</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7305</t>
+          <t>0; 6989</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 5148</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>854; 7982</t>
+          <t>861; 7510</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5721</t>
+          <t>0; 5196</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 9007</t>
+          <t>0; 9682</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6516</t>
+          <t>0; 6703</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3202; 14466</t>
+          <t>3103; 14087</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>907; 9783</t>
+          <t>0; 9971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5729</t>
+          <t>0; 5802</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7083</t>
+          <t>0; 6176</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7247</t>
+          <t>0; 6065</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>944; 9593</t>
+          <t>937; 9264</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4896; 17776</t>
+          <t>4681; 17905</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2005; 13507</t>
+          <t>2069; 12736</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>828; 8262</t>
+          <t>1055; 9554</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1046; 9531</t>
+          <t>972; 9351</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6127</t>
+          <t>0; 6456</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>798; 8112</t>
+          <t>807; 8523</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>942; 9047</t>
+          <t>964; 8903</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 6716</t>
+          <t>0; 6773</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2755; 12930</t>
+          <t>2710; 12568</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3247; 15063</t>
+          <t>3140; 14621</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1062; 9542</t>
+          <t>1068; 9243</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12841; 29474</t>
+          <t>13057; 30053</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20728; 43390</t>
+          <t>21455; 43465</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20534; 43484</t>
+          <t>20699; 42437</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6940; 21806</t>
+          <t>7051; 20533</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6521; 20973</t>
+          <t>7246; 23098</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9209; 24915</t>
+          <t>9792; 25595</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23224; 43983</t>
+          <t>22869; 44669</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30736; 57019</t>
+          <t>31715; 59310</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33082; 59840</t>
+          <t>34159; 61460</t>
         </is>
       </c>
     </row>
